--- a/data_extactor/batch_10_fa/batch_0075_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0075_fa.xlsx
@@ -513,22 +513,22 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>ساختمان و ساخت‌وساز | مکانیک | ریاضیات | ایمنی و امنیت عمومی | مدیریت و سرپرستی</t>
+          <t>ساختمان و ساخت‌وساز | مکانیک | ریاضیات | ایمنی و امنیت عمومی | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>هماهنگی چند عضو بدن | قدرت ایستا | ثبات بازو-دست | زبردستی دستی | بینایی نزدیک | تجسم فضایی | دقت کنترل | قدرت تنه | انعطاف‌پذیری گسترده | تعادل عمومی بدن | درک عمق | حساسیت به مشکل | توجه انتخابی | قدرت پویا | بینایی دور | زبردستی انگشتان | استقامت | زمان عکس‌العمل | کنترل سرعت | ترتیب‌دهی به اطلاعات | توجه شنیداری | حساسیت شنوایی | درک شفاهی | استدلال قیاسی | بیان شفاهی | هماهنگی عمومی بدن | جهت‌گیری پاسخ | وضوح گفتار | تشخیص گفتار | حساسیت به درخشندگی نور | تقسیم زمان | سرعت ادراکی | انعطاف‌پذیری دسته‌بندی | درک کتبی</t>
+          <t>هماهنگی چند عضو | قدرت ایستا | ثبات دست و بازو | مهارت دستی | بینایی نزدیک | تجسم | دقت کنترل | قدرت تنه | انعطاف‌پذیری دامنه حرکت | تعادل کلی بدن | درک عمق | حساسیت به مسئله | توجه انتخابی | قدرت پویا | بینایی دور | مهارت انگشتان | استقامت | زمان عکس‌العمل | کنترل نرخ | ترتیب‌دهی اطلاعات | توجه شنیداری | حساسیت شنوایی | درک شفاهی | استدلال قیاسی | بیان شفاهی | هماهنگی کلی بدن | جهت‌گیری پاسخ | وضوح گفتار | تشخیص گفتار | حساسیت به درخشندگی شدید | تقسیم توجه | سرعت ادراکی | انعطاف‌پذیری دسته‌بندی | درک کتبی</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا ناراحت‌کننده هستند | فضای باز، قرار گرفتن در معرض تمام شرایط آب و هوایی | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | قرار گرفتن در معرض ارتفاعات بالا | صرف زمان به صورت ایستاده | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | نزدیکی فیزیکی | پوشیدن تجهیزات حفاظتی یا ایمنی تخصصی مانند دستگاه تنفس، کمربند ایمنی، لباس‌های محافظ کامل یا محافظت در برابر تشعشع | کار با یا مشارکت در یک گروه یا تیم کاری | ارتباط با دیگران | قرار گرفتن در معرض آلاینده‌ها | سلامت و ایمنی سایر کارگران | گفتگوهای چهره به چهره با افراد و درون تیم‌ها | قرار گرفتن در معرض تجهیزات خطرناک | فشار زمانی | قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، گاز گرفتگی‌ها یا نیش‌ها | اهمیت دقیق یا درست بودن | قرار گرفتن در معرض شرایط نوری بسیار روشن یا ناکافی | پیامدهای کاری و نتایج سایر کارگران | در یک وسیله نقلیه روباز یا کار با تجهیزات | قرار گرفتن در معرض فضای کاری تنگ، موقعیت‌های بدنی نامناسب | صرف زمان برای پیاده‌روی یا دویدن | فراوانی تصمیم‌گیری | تاثیر تصمیمات بر همکاران یا نتایج شرکت | صرف زمان برای خم شدن یا چرخاندن بدن | آزادی در تصمیم‌گیری | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | سطح رقابت | پیامد خطا | صرف زمان برای انجام حرکات تکراری | تعیین وظایف، اولویت‌ها و اهداف</t>
+          <t>استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | فضای باز، در معرض تمام شرایط آب و هوایی | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | قرار گرفتن در معرض ارتفاعات بالا | صرف زمان برای ایستادن | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | نزدیکی فیزیکی | استفاده از تجهیزات حفاظتی یا ایمنی تخصصی مانند دستگاه تنفس، هارنس ایمنی، لباس‌های محافظ کامل یا محافظت در برابر تشعشع | کار با یا مشارکت در یک گروه کاری یا تیم | ارتباط با دیگران | قرار گرفتن در معرض آلاینده‌ها | سلامت و ایمنی سایر کارکنان | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | قرار گرفتن در معرض تجهیزات خطرناک | فشار زمانی | قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، گاز گرفتگی‌ها یا نیش‌ها | اهمیت دقیق یا درست بودن | قرار گرفتن در معرض شرایط نوری بسیار روشن یا ناکافی | پیامدهای کاری و نتایج سایر کارکنان | در یک وسیله نقلیه روباز یا کار با تجهیزات | قرار گرفتن در معرض فضای کاری تنگ، موقعیت‌های بدنی نامناسب | صرف زمان برای راه رفتن یا دویدن | فراوانی تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | صرف زمان برای خم کردن یا چرخاندن بدن | آزادی در تصمیم‌گیری | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | سطح رقابت | پیامد خطا | صرف زمان برای انجام حرکات تکراری | تعیین وظایف، اولویت‌ها و اهداف</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>مونتاژکنندگان سازه، سطوح، تجهیزات مهاربندی و سیستم‌های هواپیما | دیگ‌سازان | بناهای آجر و بلوک | نجاران | بناهای سیمان و پرداخت‌کاران بتن | کارگران ساختمانی | نصابان دیوار خشک و تایل سقف | دستیاران--بناهای آجر، بلوک، سنگ و نصابان کاشی و مرمر | دستیاران--لوله‌کشان، لوله‌کشان صنعتی و بخار | کارگران طرح‌بندی، فلز و پلاستیک | کارگران تعمیر و نگهداری عمومی | آسیاب‌سازان | لوله‌گذاران | لوله‌کشان، لوله‌کشان صنعتی و بخار | کارگران آهن تقویت‌کننده و میلگرد | دکل‌بندها | کارگران ورق‌کاری فلزی | سازندگان و مونتاژکنندگان فلزات سازه‌ای | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های جوشکاری، لحیم‌کاری و برنج‌کاری | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های چوب‌بری، به جز اره‌کشی</t>
+          <t>مونتاژکنندگان سازه، سطوح، تجهیزات و سیستم‌های هواپیما | دیگ‌سازان | بنّایان آجرکار و بلوک‌کار | نجّاران | بنّایان سیمان‌کار و پرداخت‌کاران بتن | کارگران ساختمانی | نصابان دیوار خشک و تایل سقف | دستیاران--بناهای آجر، بلوک، سنگ و نصابان کاشی و مرمر | دستیاران--لوله‌کشان، لوله‌کشان صنعتی و بخار | کارگران شابلون‌زنی، فلز و پلاستیک | کارگران نگهداری و تعمیرات عمومی | مهندسان نصب ماشین‌آلات | لوله‌گذاران | لوله‌کش‌ها، لوله‌کش‌های صنعتی و بخار | کارگران آهن تقویتی و میلگرد | ریگرها | کارگران ورق‌کاری | سازندگان و مونتاژکاران فلزات سازه‌ای | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های جوشکاری، لحیم‌کاری نرم و لحیم‌کاری سخت | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های چوب‌بری، به جز اره‌کشی</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -560,7 +560,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>نرم‌افزار برآورد هزینه | Extensible markup language XML | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft Word | نرم‌افزار Salesforce | نرم‌افزار زمان‌بندی کار</t>
+          <t>نرم‌افزار برآورد هزینه | زبان نشانه‌گذاری توسعه‌پذیر XML | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft Word | نرم‌افزار Salesforce | نرم‌افزار زمان‌بندی کار</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -570,22 +570,22 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>ساختمان و ساخت‌وساز | مهندسی و فناوری | مکانیک | طراحی | مدیریت و سرپرستی | خدمات مشتری و شخصی | ریاضیات | ایمنی و امنیت عمومی | آموزش و تربیت | تولید و فرآوری | زبان انگلیسی | رایانه‌ها و الکترونیک</t>
+          <t>ساختمان و ساخت‌وساز | مهندسی و فناوری | مکانیک | طراحی | مدیریت و اداره | خدمات مشتری و شخصی | ریاضیات | ایمنی و امنیت عمومی | آموزش و پرورش | تولید و فرآوری | زبان انگلیسی | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>حساسیت به مشکل | بینایی نزدیک | تجسم فضایی | ترتیب‌دهی به اطلاعات | درک شفاهی | استدلال قیاسی | ثبات بازو-دست | زبردستی دستی | زبردستی انگشتان | انعطاف‌پذیری گسترده | قدرت تنه | قدرت ایستا | هماهنگی چند عضو بدن | سرعت ادراکی | بیان شفاهی | تعادل عمومی بدن | دقت کنترل | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی</t>
+          <t>حساسیت به مسئله | بینایی نزدیک | تجسم | ترتیب‌دهی اطلاعات | درک شفاهی | استدلال قیاسی | ثبات دست و بازو | مهارت دستی | مهارت انگشتان | انعطاف‌پذیری دامنه حرکت | قدرت تنه | قدرت ایستا | هماهنگی چند عضو | سرعت ادراکی | بیان شفاهی | تعادل کلی بدن | دقت کنترل | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>گفتگوهای چهره به چهره با افراد و درون تیم‌ها | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | کار با یا مشارکت در یک گروه یا تیم کاری | فضای باز، قرار گرفتن در معرض تمام شرایط آب و هوایی | مکالمات تلفنی | صرف زمان برای استفاده از دست‌ها جهت جابجایی, کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | قرار گرفتن در معرض ارتفاعات بالا | اهمیت دقیق یا درست بودن | سلامت و ایمنی سایر کارگران | نزدیکی فیزیکی | ارتباط با دیگران | صرف زمان به صورت ایستاده | قرار گرفتن در معرض شرایط خطرناک | قرار گرفتن در معرض تجهیزات خطرناک | آزادی در تصمیم‌گیری | در یک وسیله نقلیه سرپوشیده یا کار با تجهیزات سرپوشیده | پیامدهای کاری و نتایج سایر کارگران | فراوانی تصمیم‌گیری | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | صرف زمان برای حفظ یا به دست آوردن مجدد تعادل | تعیین وظایف، اولویت‌ها و اهداف | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | پیامد خطا | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا ناراحت‌کننده هستند | تاثیر تصمیمات بر همکاران یا نتایج شرکت | داخل ساختمان، بدون کنترل شرایط محیطی | فشار زمانی | صرف زمان برای انجام حرکات تکراری | موقعیت‌های تعارض | فضای باز، زیر سرپناه | ایمیل | قرار گرفتن در معرض فضای کاری تنگ، موقعیت‌های بدنی نامناسب | اهمیت تکرار وظایف یکسان | قرار گرفتن در معرض شرایط نوری بسیار روشن یا ناکافی | صرف زمان برای زانو زدن، چمباتمه زدن، خم شدن یا خزیدن | صرف زمان برای خم شدن یا چرخاندن بدن</t>
+          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | کار با یا مشارکت در یک گروه کاری یا تیم | فضای باز، در معرض تمام شرایط آب و هوایی | مکالمات تلفنی | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | قرار گرفتن در معرض ارتفاعات بالا | اهمیت دقیق یا درست بودن | سلامت و ایمنی سایر کارکنان | نزدیکی فیزیکی | ارتباط با دیگران | صرف زمان برای ایستادن | قرار گرفتن در معرض شرایط خطرناک | قرار گرفتن در معرض تجهیزات خطرناک | آزادی در تصمیم‌گیری | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | پیامدهای کاری و نتایج سایر کارکنان | فراوانی تصمیم‌گیری | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | صرف زمان برای حفظ یا بازیابی تعادل | تعیین وظایف، اولویت‌ها و اهداف | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | پیامد خطا | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | تأثیر تصمیمات بر همکاران یا نتایج شرکت | محیط داخلی، بدون کنترل شرایط محیطی | فشار زمانی | صرف زمان برای انجام حرکات تکراری | موقعیت‌های تعارض | فضای باز، زیر سقف | ایمیل | قرار گرفتن در معرض فضای کاری تنگ، موقعیت‌های بدنی نامناسب | اهمیت تکرار وظایف یکسان | قرار گرفتن در معرض شرایط نوری بسیار روشن یا ناکافی | صرف زمان برای زانو زدن، چمباتمه زدن، خم شدن یا خزیدن | صرف زمان برای خم کردن یا چرخاندن بدن</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>تعمیرکاران موتور الکتریکی، ابزار برقی و موارد مرتبط | مهندسان برق | نصابان و تعمیرکاران تجهیزات الکتریکی و الکترونیکی، تجهیزات حمل و نقل | تعمیرکاران تجهیزات الکتریکی و الکترونیکی، تجهیزات تجاری و صنعتی | تعمیرکاران تجهیزات الکتریکی و الکترونیکی، نیروگاه، پست برق و رله | برق‌کاران | مهندسان انرژی، به جز باد و خورشید | تکنسین‌های زمین‌گرمایی | مکانیک‌ها و نصابان گرمایش، تهویه مطبوع و تبرید | تکنسین‌های نیروگاه برق‌آبی | تکنسین‌های نورپردازی | کارگران تعمیر و نگهداری عمومی | مهندسان مکانیک | لوله‌کشان، لوله‌کشان صنعتی و بخار | مدیران نصب انرژی خورشیدی | مهندسان سیستم‌های انرژی خورشیدی | نمایندگان فروش و ارزیابان خورشیدی | نصابان و تکنسین‌های حرارتی خورشیدی | مهندسان انرژی باد | تکنسین‌های خدمات توربین بادی</t>
+          <t>تعمیرکاران موتور الکتریکی، ابزار برقی و موارد مرتبط | مهندسان برق | نصب‌کنندگان و تعمیرکنندگان تجهیزات الکتریکی و الکترونیکی، تجهیزات حمل و نقل | تعمیرکنندگان تجهیزات الکتریکی و الکترونیکی، تجهیزات تجاری و صنعتی | تعمیرکنندگان تجهیزات الکتریکی و الکترونیکی، نیروگاه‌ها، پست‌های برق و رله‌ها | برق‌کاران | مهندسان انرژی، به جز باد و خورشید | تکنسین‌های زمین‌گرمایی | مکانیک‌ها و نصابان گرمایش، تهویه مطبوع و تبرید | تکنسین‌های نیروگاه برق‌آبی | تکنسین‌های نورپردازی | کارگران نگهداری و تعمیرات عمومی | مهندسان مکانیک | لوله‌کش‌ها، لوله‌کش‌های صنعتی و بخار | مدیران نصب انرژی خورشیدی | مهندسان سیستم‌های انرژی خورشیدی | نمایندگان و ارزیابان فروش تجهیزات خورشیدی | نصابان و تکنسین‌های حرارتی خورشیدی | مهندسان انرژی بادی | تکنسین‌های خدمات توربین بادی</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Autodesk Revit | Aya Associates Comp-U-Floor | CPR Visual Estimator | نرم‌افزار طراحی و ترسیم به کمک رایانه CADD | Construction Management Software ProEst | Daystar iStructural.com | EasyCAD Iris 2D | Intuit QuickBooks | Measure Square FloorEstimate Pro | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft PowerPoint | Microsoft SharePoint | Microsoft Visio | Microsoft Word | RISA Technologies RISAMasonry | TileGem | Tradesman's Software Master Estimator</t>
+          <t>Autodesk Revit | Aya Associates Comp-U-Floor | CPR Visual Estimator | نرم‌افزار طراحی و نقشه‌کشی به کمک کامپیوتر CADD | نرم‌افزار مدیریت ساخت ProEst | Daystar iStructural.com | EasyCAD Iris 2D | Intuit QuickBooks | Measure Square FloorEstimate Pro | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft PowerPoint | Microsoft SharePoint | Microsoft Visio | Microsoft Word | RISA Technologies RISAMasonry | TileGem | Tradesman's Software Master Estimator</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -632,17 +632,17 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>قدرت تنه | قدرت ایستا | هماهنگی چند عضو بدن | ثبات بازو-دست | بینایی نزدیک | انعطاف‌پذیری گسترده | بینایی دور | زبردستی دستی | تجسم فضایی | ترتیب‌دهی به اطلاعات | درک عمق | تعادل عمومی بدن | استقامت | قدرت پویا | سرعت حرکت اعضای بدن | دقت کنترل | زبردستی انگشتان | استقامت قیاسی | درک شفاهی</t>
+          <t>قدرت تنه | قدرت ایستا | هماهنگی چند عضو | ثبات دست و بازو | بینایی نزدیک | انعطاف‌پذیری دامنه حرکت | بینایی دور | مهارت دستی | تجسم | ترتیب‌دهی اطلاعات | درک عمق | تعادل کلی بدن | استقامت | قدرت پویا | سرعت حرکت اعضا | دقت کنترل | مهارت انگشتان | استدلال قیاسی | درک شفاهی</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | گفتگوهای چهره به چهره با افراد و درون تیم‌ها | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا ناراحت‌کننده هستند | فشار زمانی | قرار گرفتن در معرض آلاینده‌ها | صرف زمان به صورت ایستاده | فضای باز، قرار گرفتن در معرض تمام شرایط آب و هوایی | کار با یا مشارکت در یک گروه یا تیم کاری | صرف زمان برای انجام حرکات تکراری | قرار گرفتن در معرض ارتفاعات بالا | قرار گرفتن در معرض تجهیزات خطرناک | سلامت و ایمنی سایر کارگران | پیامدهای کاری و نتایج سایر کارگران | صرف زمان برای خم شدن یا چرخاندن بدن | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | اهمیت دقیق یا درست بودن | تعیین وظایف، اولویت‌ها و اهداف | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | نزدیکی فیزیکی | مکالمات تلفنی | صرف زمان برای بالا رفتن از نردبان‌ها، داربست‌ها یا تیرها | سطح رقابت | پوشیدن تجهیزات حفاظتی یا ایمنی تخصصی مانند دستگاه تنفس، کمربند ایمنی، لباس‌های محافظ کامل یا محافظت در برابر تشعشع | ارتباط با دیگران | صرف زمان برای پیاده‌روی یا دویدن | تاثیر تصمیمات بر همکاران یا نتایج شرکت</t>
+          <t>استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | فشار زمانی | قرار گرفتن در معرض آلاینده‌ها | صرف زمان برای ایستادن | فضای باز، در معرض تمام شرایط آب و هوایی | کار با یا مشارکت در یک گروه کاری یا تیم | صرف زمان برای انجام حرکات تکراری | قرار گرفتن در معرض ارتفاعات بالا | قرار گرفتن در معرض تجهیزات خطرناک | سلامت و ایمنی سایر کارکنان | پیامدهای کاری و نتایج سایر کارکنان | صرف زمان برای خم کردن یا چرخاندن بدن | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | اهمیت دقیق یا درست بودن | تعیین وظایف، اولویت‌ها و اهداف | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | نزدیکی فیزیکی | مکالمات تلفنی | صرف زمان برای بالا رفتن از نردبان‌ها، داربست‌ها یا تیرها | سطح رقابت | استفاده از تجهیزات حفاظتی یا ایمنی تخصصی مانند دستگاه تنفس، هارنس ایمنی، لباس‌های محافظ کامل یا محافظت در برابر تشعشع | ارتباط با دیگران | صرف زمان برای راه رفتن یا دویدن | تأثیر تصمیمات بر همکاران یا نتایج شرکت</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>بناهای آجر و بلوک | نجاران | بناهای سیمان و پرداخت‌کاران بتن | کارگران ساختمانی | نصابان دیوار خشک و تایل سقف | نصابان کف‌پوش، به جز فرش، چوب و کاشی‌های سخت | دستیاران--نجاران | دستیاران--کارگران استخراج | دستیاران--کارگران نصب، تعمیر و نگهداری | دستیاران--نقاشان، کاغذدیواری‌کن‌ها، گچ‌کاران و بناهای گچ‌بری | دستیاران--لوله‌کشان، لوله‌کشان صنعتی و بخار | دستیاران--کارگران تولید | دستیاران--سقف‌سازان | کارگران عایق‌کاری، کف، سقف و دیوار | گچ‌کاران و بناهای گچ‌بری | تعمیرکاران مواد نسوز، به جز بناهای آجر | سنگ‌تراشان | کارگران سازه‌های آهنی و فولادی | کارگران و پرداخت‌کاران ترازو | نصابان کاشی و سنگ</t>
+          <t>بنّایان آجرکار و بلوک‌کار | نجّاران | بنّایان سیمان‌کار و پرداخت‌کاران بتن | کارگران ساختمانی | نصابان دیوار خشک و تایل سقف | کفپوش‌کاران، به‌جز موکت، چوب و کاشی سخت | دستیاران--نجاران | دستیاران--کارگران استخراج | دستیاران--کارگران نصب، نگهداری و تعمیرات | دستیاران--نقاشان، کاغذدیواری‌کن‌ها، گچ‌کاران و بناهای گچ‌بری | دستیاران--لوله‌کشان، لوله‌کشان صنعتی و بخار | کمک‌کاران--کارگران تولید | دستیاران--سقف‌سازان | کارگران عایق‌کاری کف، سقف و دیوار | گچ‌کاران و بناهای سیمان‌کاری | تعمیرکاران مواد نسوز، به جز بناهای آجرکار | بنّایان سنگ‌کار | کارگران سازه‌های آهنی و فولادی | کارگران و پرداخت‌کاران ترازو | کاشی‌کاران و سنگ‌کاران</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Bosch Punch List | نرم‌افزار برآورد هزینه | Craftsman CD Estimator | نرم‌افزار ترسیم و طراحی | Intuit QuickBooks | نرم‌افزار هزینه‌یابی پروژه | Linux | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft SharePoint | Microsoft Windows | Microsoft Word | Oracle Database | Quicken | نرم‌افزار SAP | نرم‌افزار Salesforce | Turtle Creek Software Goldenseal | UNIX</t>
+          <t>Bosch Punch List | نرم‌افزار برآورد هزینه | Craftsman CD Estimator | نرم‌افزار ترسیم و طراحی | Intuit QuickBooks | نرم‌افزار هزینه‌یابی کار | Linux | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft SharePoint | Microsoft Windows | Microsoft Word | Oracle Database | Quicken | نرم‌افزار SAP | نرم‌افزار Salesforce | Turtle Creek Software Goldenseal | UNIX</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -684,22 +684,22 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>ساختمان و ساخت‌وساز | مکانیک | ریاضیات | حمل‌ونقل | زبان انگلیسی | خدمات مشتری و شخصی | تولید و فرآوری | طراحی | ایمنی و امنیت عمومی | مدیریت و سرپرستی | آموزش و تربیت | مخابرات</t>
+          <t>ساختمان و ساخت‌وساز | مکانیک | ریاضیات | حمل و نقل | زبان انگلیسی | خدمات مشتری و شخصی | تولید و فرآوری | طراحی | ایمنی و امنیت عمومی | مدیریت و اداره | آموزش و پرورش | مخابرات</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>بینایی نزدیک | ثبات بازو-دست | زبردستی دستی | حساسیت به مشکل | انعطاف‌پذیری گسترده | قدرت ایستا | هماهنگی چند عضو بدن | وضوح گفتار | تشخیص گفتار | درک عمق | قدرت تنه | زمان عکس‌العمل | دقت کنترل | زبردستی انگشتان | توجه انتخابی | تجسم فضایی | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی به اطلاعات | استدلال استقرایی | استدلال قیاسی | بیان شفاهی | درک شفاهی</t>
+          <t>بینایی نزدیک | ثبات دست و بازو | مهارت دستی | حساسیت به مسئله | انعطاف‌پذیری دامنه حرکت | قدرت ایستا | هماهنگی چند عضو | وضوح گفتار | تشخیص گفتار | درک عمق | قدرت تنه | زمان عکس‌العمل | دقت کنترل | مهارت انگشتان | توجه انتخابی | تجسم | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | استدلال استقرایی | استدلال قیاسی | بیان شفاهی | درک شفاهی</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | گفتگوهای چهره به چهره با افراد و درون تیم‌ها | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | صرف زمان به صورت ایستاده | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا ناراحت‌کننده هستند | قرار گرفتن در معرض تجهیزات خطرناک | ارتباط با دیگران | اهمیت دقیق یا درست بودن | سلامت و ایمنی سایر کارگران | فضای باز، قرار گرفتن در معرض تمام شرایط آب و هوایی | آزادی در تصمیم‌گیری | کار با یا مشارکت در یک گروه یا تیم کاری | نزدیکی فیزیکی | فشار زمانی | تعیین وظایف، اولویت‌ها و اهداف | قرار گرفتن در معرض آلاینده‌ها | صرف زمان برای انجام حرکات تکراری | مکالمات تلفنی | قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، گاز گرفتگی‌ها یا نیش‌ها | پیامدهای کاری و نتایج سایر کارگران | قرار گرفتن در معرض فضای کاری تنگ، موقعیت‌های بدنی نامناسب | پیامد خطا | صرف زمان برای خم شدن یا چرخاندن بدن | تاثیر تصمیمات بر همکاران یا نتایج شرکت | فراوانی تصمیم‌گیری | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | سطح رقابت</t>
+          <t>استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | صرف زمان برای ایستادن | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | قرار گرفتن در معرض تجهیزات خطرناک | ارتباط با دیگران | اهمیت دقیق یا درست بودن | سلامت و ایمنی سایر کارکنان | فضای باز، در معرض تمام شرایط آب و هوایی | آزادی در تصمیم‌گیری | کار با یا مشارکت در یک گروه کاری یا تیم | نزدیکی فیزیکی | فشار زمانی | تعیین وظایف، اولویت‌ها و اهداف | قرار گرفتن در معرض آلاینده‌ها | صرف زمان برای انجام حرکات تکراری | مکالمات تلفنی | قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، گاز گرفتگی‌ها یا نیش‌ها | پیامدهای کاری و نتایج سایر کارکنان | قرار گرفتن در معرض فضای کاری تنگ، موقعیت‌های بدنی نامناسب | پیامد خطا | صرف زمان برای خم کردن یا چرخاندن بدن | تأثیر تصمیمات بر همکاران یا نتایج شرکت | فراوانی تصمیم‌گیری | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | سطح رقابت</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>دیگ‌سازان | بناهای آجر و بلوک | کابینت‌سازان و نجاران کارگاهی | نجاران | بناهای سیمان و پرداخت‌کاران بتن | نصابان دیوار خشک و تایل سقف | دستیاران--بناهای آجر، بلوک، سنگ و نصابان کاشی و مرمر | دستیاران--برق‌کاران | دستیاران--کارگران استخراج | دستیاران--کارگران نصب، تعمیر و نگهداری | دستیاران--نقاشان، کاغذدیواری‌کن‌ها، گچ‌کاران و بناهای گچ‌بری | دستیاران--لوله‌کشان، لوله‌کشان صنعتی و بخار | دستیاران--کارگران تولید | دستیاران--سقف‌سازان | کارگران طرح‌بندی، فلز و پلاستیک | گچ‌کاران و بناهای گچ‌بری | کارگران آهن تقویت‌کننده و میلگرد | کارگران سازه‌های آهنی و فولادی | سازندگان و مونتاژکنندگان فلزات سازه‌ای | کارگران و پرداخت‌کاران ترازو</t>
+          <t>دیگ‌سازان | بنّایان آجرکار و بلوک‌کار | کابینت‌سازان و نجاران نیمکت | نجّاران | بنّایان سیمان‌کار و پرداخت‌کاران بتن | نصابان دیوار خشک و تایل سقف | دستیاران--بناهای آجر، بلوک، سنگ و نصابان کاشی و مرمر | دستیاران--برق‌کاران | دستیاران--کارگران استخراج | دستیاران--کارگران نصب، نگهداری و تعمیرات | دستیاران--نقاشان، کاغذدیواری‌کن‌ها، گچ‌کاران و بناهای گچ‌بری | دستیاران--لوله‌کشان، لوله‌کشان صنعتی و بخار | کمک‌کاران--کارگران تولید | دستیاران--سقف‌سازان | کارگران شابلون‌زنی، فلز و پلاستیک | گچ‌کاران و بناهای سیمان‌کاری | کارگران آهن تقویتی و میلگرد | کارگران سازه‌های آهنی و فولادی | سازندگان و مونتاژکاران فلزات سازه‌ای | کارگران و پرداخت‌کاران ترازو</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -731,7 +731,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>نرم‌افزار طراحی یا ترسیم به کمک رایانه | Microsoft Excel | نرم‌افزار Microsoft Office | نرم‌افزار بایگانی سوابق | نرم‌افزار تولید گزارش</t>
+          <t>نرم‌افزار نقشه‌کشی یا طراحی به کمک کامپیوتر | Microsoft Excel | نرم‌افزار Microsoft Office | نرم‌افزار ثبت سوابق | نرم‌افزار تولید گزارش</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -741,22 +741,22 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ساختمان و ساخت‌وساز | مکانیک | ایمنی و امنیت عمومی | طراحی | خدمات مشتری و شخصی | مدیریت و سرپرستی | آموزش و تربیت | زبان انگلیسی | ریاضیات | مهندسی و فناوری | فیزیک | حمل‌ونقل</t>
+          <t>ساختمان و ساخت‌وساز | مکانیک | ایمنی و امنیت عمومی | طراحی | خدمات مشتری و شخصی | مدیریت و اداره | آموزش و پرورش | زبان انگلیسی | ریاضیات | مهندسی و فناوری | فیزیک | حمل و نقل</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>بینایی نزدیک | زبردستی دستی | انعطاف‌پذیری گسترده | زبردستی انگشتان | ثبات بازو-دست | حساسیت به مشکل | دقت کنترل | هماهنگی چند عضو بدن | قدرت تنه | تشخیص رنگ‌های بصری | بیان شفاهی | درک شفاهی | تشخیص گفتار | توجه انتخابی | ترتیب‌دهی به اطلاعات | استدلال قیاسی | وضوح گفتار | تعادل عمومی بدن | تجسم فضایی</t>
+          <t>بینایی نزدیک | مهارت دستی | انعطاف‌پذیری دامنه حرکت | مهارت انگشتان | ثبات دست و بازو | حساسیت به مسئله | دقت کنترل | هماهنگی چند عضو | قدرت تنه | تشخیص رنگ بصری | بیان شفاهی | درک شفاهی | تشخیص گفتار | توجه انتخابی | ترتیب‌دهی اطلاعات | استدلال قیاسی | وضوح گفتار | تعادل کلی بدن | تجسم</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش, محافظ گوش، کلاه ایمنی یا جلیقه نجات | گفتگوهای چهره به چهره با افراد و درون تیم‌ها | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | صرف زمان به صورت ایستاده | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا ناراحت‌کننده هستند | کار با یا مشارکت در یک گروه یا تیم کاری | ارتباط با دیگران | قرار گرفتن در معرض فضای کاری تنگ، موقعیت‌های بدنی نامناسب | اهمیت دقیق یا درست بودن | نزدیکی فیزیکی | قرار گرفتن در معرض تجهیزات خطرناک | قرار گرفتن در معرض آلاینده‌ها | صرف زمان برای پیاده‌روی یا دویدن | فضای باز، قرار گرفتن در معرض تمام شرایط آب و هوایی | فشار زمانی | صرف زمان برای بالا رفتن از نردبان‌ها، داربست‌ها یا تیرها | صرف زمان برای انجام حرکات تکراری | داخل ساختمان، بدون کنترل شرایط محیطی | صرف زمان برای زانو زدن، چمباتمه زدن، خم شدن یا خزیدن | فضای باز، زیر سرپناه | فراوانی تصمیم‌گیری | قرار گرفتن در معرض شرایط خطرناک | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | سلامت و ایمنی سایر کارگران | آزادی در تصمیم‌گیری | مکالمات تلفنی</t>
+          <t>استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | صرف زمان برای ایستادن | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | کار با یا مشارکت در یک گروه کاری یا تیم | ارتباط با دیگران | قرار گرفتن در معرض فضای کاری تنگ، موقعیت‌های بدنی نامناسب | اهمیت دقیق یا درست بودن | نزدیکی فیزیکی | قرار گرفتن در معرض تجهیزات خطرناک | قرار گرفتن در معرض آلاینده‌ها | صرف زمان برای راه رفتن یا دویدن | فضای باز، در معرض تمام شرایط آب و هوایی | فشار زمانی | صرف زمان برای بالا رفتن از نردبان‌ها، داربست‌ها یا تیرها | صرف زمان برای انجام حرکات تکراری | محیط داخلی، بدون کنترل شرایط محیطی | صرف زمان برای زانو زدن، چمباتمه زدن، خم شدن یا خزیدن | فضای باز، زیر سقف | فراوانی تصمیم‌گیری | قرار گرفتن در معرض شرایط خطرناک | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | سلامت و ایمنی سایر کارکنان | آزادی در تصمیم‌گیری | مکالمات تلفنی</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>مونتاژکنندگان سازه، سطوح، تجهیزات مهاربندی و سیستم‌های هواپیما | دیگ‌سازان | نجاران | تعمیرکاران موتور الکتریکی، ابزار برقی و موارد مرتبط | نصابان و تعمیرکاران خطوط انتقال نیروی الکتریکی | مونتاژکنندگان تجهیزات الکتریکی و الکترونیکی | نصابان و تعمیرکاران تجهیزات الکتریکی و الکترونیکی، تجهیزات حمل و نقل | برق‌کاران | دستیاران--نجاران | دستیاران--کارگران استخراج | دستیاران--کارگران نصب، تعمیر و نگهداری | دستیاران--نقاشان، کاغذدیواری‌کن‌ها، گچ‌کاران و بناهای گچ‌بری | دستیاران--لوله‌کشان، لوله‌کشان صنعتی و بخار | تکنسین‌های نورپردازی | کارگران تعمیر و نگهداری عمومی | آسیاب‌سازان | لوله‌کشان، لوله‌کشان صنعتی و بخار | دکل‌بندها | کارگران سازه‌های آهنی و فولادی | سازندگان و مونتاژکنندگان فلزات سازه‌ای</t>
+          <t>مونتاژکنندگان سازه، سطوح، تجهیزات و سیستم‌های هواپیما | دیگ‌سازان | نجّاران | تعمیرکاران موتور الکتریکی، ابزار برقی و موارد مرتبط | نصابان و تعمیرکاران خطوط انتقال نیروی برق | مونتاژکنندگان تجهیزات الکتریکی و الکترونیکی | نصب‌کنندگان و تعمیرکنندگان تجهیزات الکتریکی و الکترونیکی، تجهیزات حمل و نقل | برق‌کاران | دستیاران--نجاران | دستیاران--کارگران استخراج | دستیاران--کارگران نصب، نگهداری و تعمیرات | دستیاران--نقاشان، کاغذدیواری‌کن‌ها، گچ‌کاران و بناهای گچ‌بری | دستیاران--لوله‌کشان، لوله‌کشان صنعتی و بخار | تکنسین‌های نورپردازی | کارگران نگهداری و تعمیرات عمومی | مهندسان نصب ماشین‌آلات | لوله‌کش‌ها، لوله‌کش‌های صنعتی و بخار | ریگرها | کارگران سازه‌های آهنی و فولادی | سازندگان و مونتاژکاران فلزات سازه‌ای</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -803,17 +803,17 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>ثبات بازو-دست | تعادل عمومی بدن | انعطاف‌پذیری گسترده | قدرت تنه | قدرت ایستا | زبردستی دستی | هماهنگی عمومی بدن | هماهنگی چند عضو بدن | تشخیص گفتار | بینایی دور | بینایی نزدیک | استقامت | قدرت پویا | زبردستی انگشتان | بیان شفاهی | درک شفاهی</t>
+          <t>ثبات دست و بازو | تعادل کلی بدن | انعطاف‌پذیری دامنه حرکت | قدرت تنه | قدرت ایستا | مهارت دستی | هماهنگی کلی بدن | هماهنگی چند عضو | تشخیص گفتار | بینایی دور | بینایی نزدیک | استقامت | قدرت پویا | مهارت انگشتان | بیان شفاهی | درک شفاهی</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>گفتگوهای چهره به چهره با افراد و درون تیم‌ها | کار با یا مشارکت در یک گروه یا تیم کاری | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | صرف زمان به صورت ایستاده | ارتباط با دیگران | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | صرف زمان برای انجام حرکات تکراری | فضای باز، قرار گرفتن در معرض تمام شرایط آب و هوایی | فراوانی تصمیم‌گیری | صرف زمان برای خم شدن یا چرخاندن بدن | فشار زمانی | سلامت و ایمنی سایر کارگران | مکالمات تلفنی | صرف زمان برای بالا رفتن از نردبان‌ها، داربست‌ها یا تیرها | قرار گرفتن در معرض ارتفاعات بالا | تاثیر تصمیمات بر همکاران یا نتایج شرکت</t>
+          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | صرف زمان برای ایستادن | ارتباط با دیگران | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | صرف زمان برای انجام حرکات تکراری | فضای باز، در معرض تمام شرایط آب و هوایی | فراوانی تصمیم‌گیری | صرف زمان برای خم کردن یا چرخاندن بدن | فشار زمانی | سلامت و ایمنی سایر کارکنان | مکالمات تلفنی | صرف زمان برای بالا رفتن از نردبان‌ها، داربست‌ها یا تیرها | قرار گرفتن در معرض ارتفاعات بالا | تأثیر تصمیمات بر همکاران یا نتایج شرکت</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Brickmasons and Blockmasons | نجاران | بناهای سیمان و پرداخت‌کاران بتن | کارگران ساختمانی | نصابان دیوار خشک و تایل سقف | دستیاران--بناهای آجر، بلوک، سنگ و نصابان کاشی و مرمر | دستیاران--نجاران | دستیاران--برق‌کاران | دستیاران--کارگران استخراج | دستیاران--کارگران نصب، تعمیر و نگهداری | دستیاران--لوله‌کشان، لوله‌کشان صنعتی و بخار | دستیاران--کارگران تولید | دستیاران--سقف‌سازان | کارگران عایق‌کاری، کف، سقف و دیوار | نقاشان، ساختمان و نگهداری | کارگران نقاشی، پوشش‌دهی و تزئین | کاغذدیواری‌کن‌ها | گچ‌کاران و بناهای گچ‌بری | سقف‌سازان | کارگران و پرداخت‌کاران ترازو</t>
+          <t>بنّایان آجرکار و بلوک‌کار | نجّاران | بنّایان سیمان‌کار و پرداخت‌کاران بتن | کارگران ساختمانی | نصابان دیوار خشک و تایل سقف | دستیاران--بناهای آجر، بلوک، سنگ و نصابان کاشی و مرمر | دستیاران--نجاران | دستیاران--برق‌کاران | دستیاران--کارگران استخراج | دستیاران--کارگران نصب، نگهداری و تعمیرات | دستیاران--لوله‌کشان، لوله‌کشان صنعتی و بخار | کمک‌کاران--کارگران تولید | دستیاران--سقف‌سازان | کارگران عایق‌کاری کف، سقف و دیوار | نقاشان، ساختمان و نگهداری | کارگران نقاشی، پوشش‌دهی و تزیین | کاغذدیواری‌کن‌ها | گچ‌کاران و بناهای سیمان‌کاری | سقف‌سازان | کارگران و پرداخت‌کاران ترازو</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -855,22 +855,22 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ساختمان و ساخت‌وساز | خدمات مشتری و شخصی | مکانیک | ریاضیات | زبان انگلیسی | مدیریت و سرپرستی</t>
+          <t>ساختمان و ساخت‌وساز | خدمات مشتری و شخصی | مکانیک | ریاضیات | زبان انگلیسی | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>زبردستی دستی | هماهنگی چند عضو بدن | ثبات بازو-دست | قدرت تنه | انعطاف‌پذیری گسترده | بینایی نزدیک | درک شفاهی | حساسیت به مشکل | تجسم فضایی | تشخیص گفتار | قدرت ایستا | دقت کنترل | زبردستی انگشتان | ترتیب‌دهی به اطلاعات | بیان شفاهی</t>
+          <t>مهارت دستی | هماهنگی چند عضو | ثبات دست و بازو | قدرت تنه | انعطاف‌پذیری دامنه حرکت | بینایی نزدیک | درک شفاهی | حساسیت به مسئله | تجسم | تشخیص گفتار | قدرت ایستا | دقت کنترل | مهارت انگشتان | ترتیب‌دهی اطلاعات | بیان شفاهی</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | فضای باز، قرار گرفتن در معرض تمام شرایط آب و هوایی | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | در یک وسیله نقلیه سرپوشیده یا کار با تجهیزات سرپوشیده | صرف زمان به صورت ایستاده | گفتگوهای چهره به چهره با افراد و درون تیم‌ها | ارتباط با دیگران | صرف زمان برای خم شدن یا چرخاندن بدن | قرار گرفتن در معرض فضای کاری تنگ، موقعیت‌های بدنی نامناسب | کار با یا مشارکت در یک گروه یا تیم کاری | فشار زمانی | صرف زمان برای زانو زدن، چمباتمه زدن، خم شدن یا خزیدن | فراوانی تصمیم‌گیری | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | صرف زمان برای انجام حرکات تکراری | نزدیکی فیزیکی | داخل ساختمان، بدون کنترل شرایط محیطی | مکالمات تلفنی | قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، گاز گرفتگی‌ها یا نیش‌ها | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا ناراحت‌کننده هستند | اهمیت دقیق یا درست بودن</t>
+          <t>صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | فضای باز، در معرض تمام شرایط آب و هوایی | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | صرف زمان برای ایستادن | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ارتباط با دیگران | صرف زمان برای خم کردن یا چرخاندن بدن | قرار گرفتن در معرض فضای کاری تنگ، موقعیت‌های بدنی نامناسب | کار با یا مشارکت در یک گروه کاری یا تیم | فشار زمانی | صرف زمان برای زانو زدن، چمباتمه زدن، خم شدن یا خزیدن | فراوانی تصمیم‌گیری | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | صرف زمان برای انجام حرکات تکراری | نزدیکی فیزیکی | محیط داخلی، بدون کنترل شرایط محیطی | مکالمات تلفنی | قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، گاز گرفتگی‌ها یا نیش‌ها | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | اهمیت دقیق یا درست بودن</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>دیگ‌سازان | نجاران | کارگران ساختمانی | نصابان دیوار خشک و تایل سقف | برق‌کاران | دستیاران--بناهای آجر، بلوک، سنگ و نصابان کاشی و مرمر | دستیاران--نجاران | دستیاران--برق‌کاران | دستیاران--کارگران استخراج | دستیاران--کارگران نصب، تعمیر و نگهداری | دستیاران--نقاشان، کاغذدیواری‌کن‌ها، گچ‌کاران و بناهای گچ‌بری | دستیاران--سقف‌سازان | کارگران عایق‌کاری، کف، سقف و دیوار | کارگران تعمیر و نگهداری عمومی | آسیاب‌سازان | لوله‌گذاران | لوله‌کشان، لوله‌کشان صنعتی و بخار | سرویس‌کاران سپتیک تانک و پاک‌کنندگان لوله فاضلاب | کارگران ورق‌کاری فلزی | کارگران سازه‌های آهنی و فولادی</t>
+          <t>دیگ‌سازان | نجّاران | کارگران ساختمانی | نصابان دیوار خشک و تایل سقف | برق‌کاران | دستیاران--بناهای آجر، بلوک، سنگ و نصابان کاشی و مرمر | دستیاران--نجاران | دستیاران--برق‌کاران | دستیاران--کارگران استخراج | دستیاران--کارگران نصب، نگهداری و تعمیرات | دستیاران--نقاشان، کاغذدیواری‌کن‌ها، گچ‌کاران و بناهای گچ‌بری | دستیاران--سقف‌سازان | کارگران عایق‌کاری کف، سقف و دیوار | کارگران نگهداری و تعمیرات عمومی | مهندسان نصب ماشین‌آلات | لوله‌گذاران | لوله‌کش‌ها، لوله‌کش‌های صنعتی و بخار | سرویس‌کاران سپتیک تانک و پاک‌کنندگان لوله‌های فاضلاب | کارگران ورق‌کاری | کارگران سازه‌های آهنی و فولادی</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>AppliCad Roof Wizard | DigiTools Roof CAD | نرم‌افزار ارزیابی هزینه انرژی | Exele TopView | نرم‌افزار محاسبه رطوبت و حرکت بخار | Insight Direct ServiceCEO | نرم‌افزار ثبت سوابق نگهداری | Roof Pro Estimate Software Roof Pro | RoofLogic | Roofing Calculator | Wintac Pro | Ziatek RoofDraw</t>
+          <t>AppliCad Roof Wizard | DigiTools Roof CAD | Energy cost evaluation software | Exele TopView | Humidity and vapor drive calculation software | Insight Direct ServiceCEO | نرم‌افزار ثبت تعمیر و نگهداری | Roof Pro Estimate Software Roof Pro | RoofLogic | Roofing Calculator | Wintac Pro | Ziatek RoofDraw</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -912,22 +912,22 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ساختمان و ساخت‌وساز | مدیریت و سرپرستی | خدمات مشتری و شخصی | ایمنی و امنیت عمومی | ریاضیات | حمل‌ونقل | مکانیک | آموزش و تربیت</t>
+          <t>ساختمان و ساخت‌وساز | مدیریت و اداره | خدمات مشتری و شخصی | ایمنی و امنیت عمومی | ریاضیات | حمل و نقل | مکانیک | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>قدرت تنه | تعادل عمومی بدن | زبردستی دستی | هماهنگی چند عضو بدن | وضوح گفتار | حساسیت به مشکل | تجسم فضایی | ثبات بازو-دست | زبردستی انگشتان | تشخیص گفتار | درک عمق | انعطاف‌پذیری گسترده | قدرت ایستا | بینایی دور | هماهنگی عمومی بدن | استقامت | انعطاف‌پذیری بستار | ترتیب‌دهی به اطلاعات | بیان شفاهی | درک شفاهی</t>
+          <t>قدرت تنه | تعادل کلی بدن | مهارت دستی | هماهنگی چند عضو | وضوح گفتار | حساسیت به مسئله | تجسم | ثبات دست و بازو | مهارت انگشتان | تشخیص گفتار | درک عمق | انعطاف‌پذیری دامنه حرکت | قدرت ایستا | بینایی دور | هماهنگی کلی بدن | استقامت | انعطاف‌پذیری بستار | ترتیب‌دهی اطلاعات | بیان شفاهی | درک شفاهی</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | صرف زمان به صورت ایستاده | قرار گرفتن در معرض ارتفاعات بالا | فضای باز، قرار گرفتن در معرض تمام شرایط آب و هوایی | گفتگوهای چهره به چهره با افراد و درون تیم‌ها | سلامت و ایمنی سایر کارگران | کار با یا مشارکت در یک گروه یا تیم کاری | صرف زمان برای زانو زدن، چمباتمه زدن، خم شدن یا خزیدن | اهمیت دقیق یا درست بودن | صرف زمان برای خم شدن یا چرخاندن بدن | قرار گرفتن در معرض آلاینده‌ها | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | صرف زمان برای انجام حرکات تکراری | تاثیر تصمیمات بر همکاران یا نتایج شرکت | صرف زمان برای پیاده‌روی یا دویدن | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا ناراحت‌کننده هستند | پیامد خطا | قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، گاز گرفتگی‌ها یا نیش‌ها | ارتباط با دیگران</t>
+          <t>صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | صرف زمان برای ایستادن | قرار گرفتن در معرض ارتفاعات بالا | فضای باز، در معرض تمام شرایط آب و هوایی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | سلامت و ایمنی سایر کارکنان | کار با یا مشارکت در یک گروه کاری یا تیم | صرف زمان برای زانو زدن، چمباتمه زدن، خم شدن یا خزیدن | اهمیت دقیق یا درست بودن | صرف زمان برای خم کردن یا چرخاندن بدن | قرار گرفتن در معرض آلاینده‌ها | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | صرف زمان برای انجام حرکات تکراری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | صرف زمان برای راه رفتن یا دویدن | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | پیامد خطا | قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، گاز گرفتگی‌ها یا نیش‌ها | ارتباط با دیگران</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>نجاران | بناهای سیمان و پرداخت‌کاران بتن | کارگران ساختمانی | نصابان دیوار خشک و تایل سقف | نصابان کف‌پوش، به جز فرش، چوب و کاشی‌های سخت | دستیاران--بناهای آجر، بلوک، سنگ و نصابان کاشی و مرمر | دستیاران--نجاران | دستیاران--برق‌کاران | دستیاران--کارگران استخراج | دستیاران--کارگران نصب، تعمیر و نگهداری | دستیاران--نقاشان، کاغذدیواری‌کن‌ها، گچ‌کاران و بناهای گچ‌بری | دستیاران--لوله‌کشان، لوله‌کشان صنعتی و بخار | کارگران عایق‌کاری، کف، سقف و دیوار | کارگران عایق‌کاری، مکانیکی | نقاشان، ساختمان و نگهداری | گچ‌کاران و بناهای گچ‌بری | سقف‌سازان | کارگران سازه‌های آهنی و فولادی | کارگران و پرداخت‌کاران ترازو | نصابان کاشی و سنگ</t>
+          <t>نجّاران | بنّایان سیمان‌کار و پرداخت‌کاران بتن | کارگران ساختمانی | نصابان دیوار خشک و تایل سقف | کفپوش‌کاران، به‌جز موکت، چوب و کاشی سخت | دستیاران--بناهای آجر، بلوک، سنگ و نصابان کاشی و مرمر | دستیاران--نجاران | دستیاران--برق‌کاران | دستیاران--کارگران استخراج | دستیاران--کارگران نصب، نگهداری و تعمیرات | دستیاران--نقاشان، کاغذدیواری‌کن‌ها، گچ‌کاران و بناهای گچ‌بری | دستیاران--لوله‌کشان، لوله‌کشان صنعتی و بخار | کارگران عایق‌کاری کف، سقف و دیوار | کارگران عایق‌کاری، مکانیکی | نقاشان، ساختمان و نگهداری | گچ‌کاران و بناهای سیمان‌کاری | سقف‌سازان | کارگران سازه‌های آهنی و فولادی | کارگران و پرداخت‌کاران ترازو | کاشی‌کاران و سنگ‌کاران</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -974,17 +974,17 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>زبردستی دستی | زبردستی انگشتان | ثبات بازو-دست | هماهنگی چند عضو بدن | دقت کنترل | قدرت ایستا | قدرت تنه | استقامت | بینایی نزدیک | بینایی دور | درک عمق | هماهنگی عمومی بدن | تعادل عمومی بدن | انعطاف‌پذیری گسترده | زمان عکس‌العمل | حساسیت به مشکل | درک شفاهی | توجه انتخابی</t>
+          <t>مهارت دستی | مهارت انگشتان | ثبات دست و بازو | هماهنگی چند عضو | دقت کنترل | قدرت ایستا | قدرت تنه | استقامت | بینایی نزدیک | بینایی دور | درک عمق | هماهنگی کلی بدن | تعادل کلی بدن | انعطاف‌پذیری دامنه حرکت | زمان عکس‌العمل | حساسیت به مسئله | درک شفاهی | توجه انتخابی</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>فضای باز، قرار گرفتن در معرض تمام شرایط آب و هوایی | صرف زمان به صورت ایستاده | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | قرار گرفتن در معرض آلاینده‌ها | قرار گرفتن در معرض تجهیزات خطرناک | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا ناراحت‌کننده هستند | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | صرف زمان برای خم شدن یا چرخاندن بدن | صرف زمان برای زانو زدن، چمباتمه زدن، خم شدن یا خزیدن | صرف زمان برای بالا رفتن از نردبان‌ها، داربست‌ها یا تیرها | قرار گرفتن در معرض ارتفاعات بالا | سلامت و ایمنی سایر کارگران | نزدیکی فیزیکی | کار با یا مشارکت در یک گروه یا تیم کاری | گفتگوهای چهره به چهره با افراد و درون تیم‌ها | اهمیت دقیق یا درست بودن | پیامد خطا | صرف زمان برای پیاده‌روی یا دویدن | قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، گاز گرفتگی‌ها یا نیش‌ها</t>
+          <t>فضای باز، در معرض تمام شرایط آب و هوایی | صرف زمان برای ایستادن | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | قرار گرفتن در معرض آلاینده‌ها | قرار گرفتن در معرض تجهیزات خطرناک | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | صرف زمان برای خم کردن یا چرخاندن بدن | صرف زمان برای زانو زدن، چمباتمه زدن، خم شدن یا خزیدن | صرف زمان برای بالا رفتن از نردبان‌ها، داربست‌ها یا تیرها | قرار گرفتن در معرض ارتفاعات بالا | سلامت و ایمنی سایر کارکنان | نزدیکی فیزیکی | کار با یا مشارکت در یک گروه کاری یا تیم | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | اهمیت دقیق یا درست بودن | پیامد خطا | صرف زمان برای راه رفتن یا دویدن | قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، گاز گرفتگی‌ها یا نیش‌ها</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>دستیاران--نجاران | دستیاران--برق‌کاران | دستیاران--لوله‌کشان، لوله‌کشان صنعتی و بخار | دستیاران--سقف‌سازان | دستیاران--نقاشان، کاغذدیواری‌کن‌ها، گچ‌کاران و بناهای گچ‌بری | دستیاران--بناهای آجر، بلوک، سنگ و نصابان کاشی و مرمر | کارگران ساختمانی | نجاران | برق‌کاران | لوله‌کشان، لوله‌کشان صنعتی و بخار | کارگران ورق‌کاری فلزی | شیشه‌بران | سقف‌سازان | کارگران عایق‌کاری، مکانیکی | کارگران سازه‌های آهنی و فولادی | کارگران آهن تقویت‌کننده و میلگرد | نصابان دیوار خشک و تایل سقف | نقاشان، ساختمان و نگهداری | سرپرستان رده اول مشاغل ساختمانی و کارگران استخراج | دستیاران--کارگران نصب، تعمیر و نگهداری</t>
+          <t>دستیاران--نجاران | دستیاران--برق‌کاران | دستیاران--لوله‌کشان، لوله‌کشان صنعتی و بخار | دستیاران--سقف‌سازان | دستیاران--نقاشان، کاغذدیواری‌کن‌ها، گچ‌کاران و بناهای گچ‌بری | دستیاران--بناهای آجر، بلوک، سنگ و نصابان کاشی و مرمر | کارگران ساختمانی | نجّاران | برق‌کاران | لوله‌کش‌ها، لوله‌کش‌های صنعتی و بخار | کارگران ورق‌کاری | شیشه‌بران | سقف‌سازان | کارگران عایق‌کاری، مکانیکی | کارگران سازه‌های آهنی و فولادی | کارگران آهن تقویتی و میلگرد | نصابان دیوار خشک و تایل سقف | نقاشان، ساختمان و نگهداری | سرپرستان خط اول مشاغل ساختمانی و کارگران استخراج | دستیاران--کارگران نصب، نگهداری و تعمیرات</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,27 +1021,27 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | گوش دادن فعال | سخن گفتن | نگارش | یادگیری فعال | نظارت | استراتژی‌های یادگیری | ریاضیات</t>
+          <t>درک مطلب | تفکر انتقادی | گوش دادن فعال | سخن گفتن | نگارش | یادگیری فعال | نظارت | راهبردهای یادگیری | ریاضیات</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ساختمان و ساخت‌وساز | ایمنی و امنیت عمومی | زبان انگلیسی | خدمات مشتری و شخصی | طراحی | قانون و حکومت | ریاضیات | مدیریت و سرپرستی | مکانیک | اداری | رایانه‌ها و الکترونیک | مهندسی و فناوری | آموزش و تربیت</t>
+          <t>ساختمان و ساخت‌وساز | ایمنی و امنیت عمومی | زبان انگلیسی | خدمات مشتری و شخصی | طراحی | قانون و دولت | ریاضیات | مدیریت و اداره | مکانیک | اداری | رایانه و الکترونیک | مهندسی و فناوری | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>حساسیت به مشکل | درک کتبی | بیان شفاهی | استدلال استقرایی | استدلال قیاسی | درک شفاهی | بیان کتبی | بینایی نزدیک | تشخیص گفتار | وضوح گفتار | ترتیب‌دهی به اطلاعات | بینایی دور | توجه انتخابی | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | تشخیص رنگ‌های بصری | تجسم فضایی | سرعت ادراکی | روان بودن ایده‌ها</t>
+          <t>حساسیت به مسئله | درک کتبی | بیان شفاهی | استدلال استقرایی | استدلال قیاسی | درک شفاهی | بیان کتبی | بینایی نزدیک | تشخیص گفتار | وضوح گفتار | ترتیب‌دهی اطلاعات | بینایی دور | توجه انتخابی | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | تشخیص رنگ بصری | تجسم | سرعت ادراکی | روانی ایده‌ها</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>ایمیل | مکالمات تلفنی | گفتگوهای چهره به چهره با افراد و درون تیم‌ها | آزادی در تصمیم‌گیری | در یک وسیله نقلیه سرپوشیده یا کار با تجهیزات سرپوشیده | فضای باز، قرار گرفتن در معرض تمام شرایط آب و هوایی | برخورد با مشتریان خارجی یا عموم مردم به طور کلی | ارتباط با دیگران | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | داخل ساختمان، بدون کنترل شرایط محیطی | اهمیت دقیق یا درست بودن | فشار زمانی | فراوانی تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | کار با یا مشارکت در یک گروه یا تیم کاری | نامه‌ها و یادداشت‌های کتبی | داخل ساختمان، با کنترل شرایط محیطی | تاثیر تصمیمات بر همکاران یا نتایج شرکت | فضای باز، زیر سرپناه | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا ناراحت‌کننده هستند | نزدیکی فیزیکی | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | موقعیت‌های تعارض</t>
+          <t>ایمیل | مکالمات تلفنی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | آزادی در تصمیم‌گیری | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | فضای باز، در معرض تمام شرایط آب و هوایی | تعامل با مشتریان خارجی یا عموم مردم | ارتباط با دیگران | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | محیط داخلی، بدون کنترل شرایط محیطی | اهمیت دقیق یا درست بودن | فشار زمانی | فراوانی تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | کار با یا مشارکت در یک گروه کاری یا تیم | نامه‌ها و یادداشت‌های کتبی | محیط داخلی، دارای کنترل شرایط محیطی | تأثیر تصمیمات بر همکاران یا نتایج شرکت | فضای باز، زیر سقف | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | نزدیکی فیزیکی | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | موقعیت‌های تعارض</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>معماران، به جز منظر و دریایی | بازرسان هوانوردی | تکنسین‌ها و فناوران مهندسی عمران | مهندسان عمران | مدیران ساخت‌وساز | برق‌کاران | ممیزان انرژی | بازرسان انطباق محیطی | مهندسان پیشگیری و حفاظت از آتش‌سوزی | سرپرستان رده اول مشاغل ساختمانی و کارگران استخراج | بازرسان و محققان اموال دولتی | مهندسان بهداشت و ایمنی کار، به جز مهندسان و بازرسان ایمنی معدن | مهندسان صنایع | بازرسان، تست‌کنندگان، سورترها، نمونه‌برداران و توزین‌کنندگان | کارگران تعمیر و نگهداری عمومی | متخصصان بهداشت و ایمنی حرفه‌ای | لوله‌کشان، لوله‌کشان صنعتی و بخار | مدیران نصب انرژی خورشیدی | بازرسان حمل‌ونقل | بازرسان وسایل نقلیه، تجهیزات و سیستم‌های حمل‌ونقل، به جز هوانوردی</t>
+          <t>معماران، به‌جز منظر و دریایی | بازرسان هوانوردی | تکنسین‌ها و کارشناسان مهندسی عمران | مهندسان عمران | مدیران ساخت‌وساز | برق‌کاران | بازرسان انرژی | بازرسان انطباق زیست‌محیطی | مهندسان پیشگیری و حفاظت از آتش‌سوزی | سرپرستان خط اول مشاغل ساختمانی و کارگران استخراج | بازرسان و محققان اموال دولتی | مهندسان بهداشت و ایمنی، به جز مهندسان و بازرسان ایمنی معدن | مهندسان صنایع | بازرسان، آزمایش‌کنندگان، سورترها، نمونه‌برداران و توزین‌کنندگان | کارگران نگهداری و تعمیرات عمومی | متخصصان بهداشت و ایمنی شغلی | لوله‌کش‌ها، لوله‌کش‌های صنعتی و بخار | مدیران نصب انرژی خورشیدی | بازرسان حمل‌ونقل | بازرسان وسایل نقلیه، تجهیزات و سیستم‌های حمل‌ونقل، به جز هوانوردی</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">

--- a/data_extactor/batch_10_fa/batch_0075_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0075_fa.xlsx
@@ -508,17 +508,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>شنیدن فعال | تفکر انتقادی | نظارت | یادگیری فعال | سخن گفتن</t>
+          <t>گوش دادن فعال | تفکر انتقادی | نظارت | یادگیری فعال | سخن گفتن</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>ساخت‌وساز و ابنیه | مکانیک | ریاضیات | ایمنی و امنیت عمومی | مدیریت و امور اداری</t>
+          <t>ساختمان و ساخت‌وساز | مکانیک | ریاضیات | ایمنی و امنیت عمومی | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>هماهنگی چنداندامی | استحکام ایستا | پایداری دست و بازو | چابکی دستی | دید نزدیک | تجسم فضایی | دقت کنترل | استحکام بالاتنه | دامنه انعطاف‌پذیری | تعادل عمومی بدن | ادراک عمق | حساسیت به مسئله | توجه انتخابی | استحکام پویا | دید دور | چابکی انگشتان | استقامت بدنی | زمان واکنش | کنترل نرخ حرکت | مرتب‌سازی اطلاعات | توجه شنیداری | حساسیت شنوایی | درک شفاهی | استدلال قیاسی | بیان شفاهی | هماهنگی عمومی بدن | جهت‌گیری پاسخ | وضوح گفتار | تشخیص گفتار | حساسیت به تابش نور | تسهیم توجه | سرعت ادراک | انعطاف‌پذیری طبقه‌بندی | درک کتبی</t>
+          <t>هماهنگی چند عضو | قدرت ایستا | ثبات دست و بازو | مهارت دستی | بینایی نزدیک | تجسم | دقت کنترل | قدرت تنه | انعطاف‌پذیری دامنه حرکت | تعادل کلی بدن | درک عمق | حساسیت به مسئله | توجه انتخابی | قدرت پویا | بینایی دور | مهارت انگشتان | استقامت | زمان عکس‌العمل | کنترل نرخ | ترتیب‌دهی اطلاعات | توجه شنیداری | حساسیت شنوایی | درک شفاهی | استدلال قیاسی | بیان شفاهی | هماهنگی کلی بدن | جهت‌گیری پاسخ | وضوح گفتار | تشخیص گفتار | حساسیت به درخشندگی شدید | تقسیم توجه | سرعت ادراکی | انعطاف‌پذیری دسته‌بندی | درک کتبی</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>مونتاژکاران سازه، سطوح، مهاربندی و سیستم‌های هواپیما | دیگ‌سازان صنعتی | بناها و بلوک‌چین‌ها | نجاران | بناهای سیمان‌کار و پرداخت‌کاران بتن | کارگران ساختمانی | نصابان صفحات گچی و تایل سقف | کمک‌بناها، کمک‌بلوک‌چین‌ها، کمک‌سنگ‌تراشان و کمک‌نصابان کاشی و مرمر | کمک‌لوله‌گذاران، کمک‌لوله‌کش‌ها، کمک‌نصابان لوله و بخار | خط‌کشان و علامت‌گذاران فلز و پلاستیک | کارگران عمومی تعمیرات و نگهداری | نصابان و مستقرکنندگان ماشین‌آلات صنعتی (میلرایت‌ها) | لوله‌گذاران | لوله‌کش‌ها، نصابان لوله‌های صنعتی و تأسیسات بخار | آرماتوربندان و نصابان میلگرد سازه | دکل‌بندان و طناب‌کاران | ورق‌کاران فلزی | سازندگان و مونتاژکاران قطعات فلزی سازه | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌آلات جوشکاری، لحیم‌کاری سخت و نرم | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌آلات نجاری به جز اره‌ها</t>
+          <t>مونتاژکاران سازه، سطوح، مهاربندی و سیستم‌های هواپیما | دیگ‌سازان و مخزن‌سازان صنعتی | بنایان و سفت‌کاران ساختمان | نجاران و درودگران | بتن‌ریزان و پرداخت‌کاران بتن | کارگران ساختمانی | نصابان دیوار کاذب و تایل سقف | کمک‌بناها، کمک‌بلوک‌چین‌ها، کمک‌سنگ‌تراشان و کمک‌نصابان کاشی و مرمر | کمک‌لوله‌گذاران، کمک‌لوله‌کش‌ها، کمک‌نصابان لوله و بخار | خط‌کش‌ها و نشانه‌گذاران قطعات فلزی و پلاستیکی | کارگران عمومی تعمیرات و نگهداری تاسیسات | ماشین‌سازان و متخصصان نصب ماشین‌آلات سنگین [میل‌رایت] | لوله‌گذاران خطوط انتقال | لوله‌کش‌ها، لوله‌کش‌های صنعتی و نصابان خطوط بخار | آرماتوربندان و نصابان میلگرد | ریگرها و تکنسین‌های مهاربندی و جابه‌جایی بار | کارگران ورق‌کاری فلزی | سازندگان و مونتاژکاران سازه‌های فلزی | تنظیم‌کاران و اپراتورهای دستگاه‌های جوشکاری و لحیم‌کاری | تنظیم‌کنندگان، متصدیان و اپراتورهای ماشین‌آلات صنایع چوب به‌جز اره</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,17 +565,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | شنیدن فعال | نظارت | درک مطلب | یادگیری فعال</t>
+          <t>تفکر انتقادی | گوش دادن فعال | نظارت | درک مطلب | یادگیری فعال</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>ساخت‌وساز و ابنیه | مهندسی و فناوری | مکانیک | طراحی | مدیریت و امور اداری | خدمات مشتریان و خدمات فردی | ریاضیات | ایمنی و امنیت عمومی | آموزش و تدریس | تولید و فرآوری | زبان انگلیسی | رایانه و الکترونیک</t>
+          <t>ساختمان و ساخت‌وساز | مهندسی و فناوری | مکانیک | طراحی | مدیریت و اداره | خدمات مشتری و شخصی | ریاضیات | ایمنی و امنیت عمومی | آموزش و پرورش | تولید و فرآوری | زبان انگلیسی | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | دید نزدیک | تجسم فضایی | مرتب‌سازی اطلاعات | درک شفاهی | استدلال قیاسی | پایداری دست و بازو | چابکی دستی | چابکی انگشتان | دامنه انعطاف‌پذیری | استحکام بالاتنه | استحکام ایستا | هماهنگی چنداندامی | سرعت ادراک | بیان شفاهی | تعادل عمومی بدن | دقت کنترل | توجه انتخابی | انعطاف‌پذیری طبقه‌بندی | استدلال استقرایی</t>
+          <t>حساسیت به مسئله | بینایی نزدیک | تجسم | ترتیب‌دهی اطلاعات | درک شفاهی | استدلال قیاسی | ثبات دست و بازو | مهارت دستی | مهارت انگشتان | انعطاف‌پذیری دامنه حرکت | قدرت تنه | قدرت ایستا | هماهنگی چند عضو | سرعت ادراکی | بیان شفاهی | تعادل کلی بدن | دقت کنترل | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>تعمیرکاران الکتروموتورها، ابزارهای برقی و تجهیزات وابسته | مهندسان برق | نصابان و تعمیرکاران تجهیزات الکتریکی و الکترونیکی ادوات حمل‌ونقل | تعمیرکاران تجهیزات الکتریکی و الکترونیکی تجاری و صنعتی | تعمیرکاران الکتریکی و الکترونیکی نیروگاه‌ها، پست‌ها و رله‌ها | برق‌کاران | مهندسان انرژی به جز باد و خورشید | تکنسین‌های زمین‌گرمایی | مکانیک‌ها و نصابان سیستم‌های سرمایشی، گرمایشی و تهویه مطبوع | تکنسین‌های نیروگاه‌های برق‌آبی | تکنسین‌های روشنایی | کارگران عمومی تعمیرات و نگهداری | مهندسان مکانیک | لوله‌کش‌ها، نصابان لوله‌های صنعتی و تأسیسات بخار | مدیران پروژه‌های نصب انرژی خورشیدی | مهندسان سیستم‌های انرژی خورشیدی | کارشناسان ارزیابی و فروش تجهیزات خورشیدی | نصابان و تکنسین‌های سیستم‌های حرارتی خورشیدی | مهندسان انرژی بادی | تکنسین‌های تعمیر و نگهداری توربین‌های بادی</t>
+          <t>تعمیرکاران موتورهای الکتریکی، ابزارهای برقی و تجهیزات وابسته | مهندسان برق | نصاب و تعمیرکار تجهیزات الکتریکی و الکترونیکی وسایل نقلیه | تعمیرکار تجهیزات الکتریکی و الکترونیکی صنعتی و تجاری | تعمیرکار تجهیزات الکتریکی نیروگاه، پست برق و رله | برق‌کاران | مهندسان انرژی، به‌جز بادی و خورشیدی | تکنسین‌های سامانه‌های زمین‌گرمایی | مکانیک‌ها و نصابان سیستم‌های گرمایشی، تهویه مطبوع و تبرید | تکنسین‌های نیروگاه برقابی | تکنسین‌های نورپردازی | کارگران عمومی تعمیرات و نگهداری تاسیسات | مهندسان مکانیک | لوله‌کش‌ها، لوله‌کش‌های صنعتی و نصابان خطوط بخار | مدیران اجرای پروژه‌های انرژی خورشیدی | مهندسان سیستم‌های انرژی خورشیدی | کارشناسان فروش و ارزیابان سامانه‌های خورشیدی | نصابان و تکنسین‌های سیستم‌های خورشیدی حرارتی | مهندسان انرژی باد | تکنسین‌های تعمیر و نگهداری توربین‌های بادی</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -627,12 +627,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>ساخت‌وساز و ابنیه | مکانیک | طراحی | ریاضیات</t>
+          <t>ساختمان و ساخت‌وساز | مکانیک | طراحی | ریاضیات</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>استحکام بالاتنه | استحکام ایستا | هماهنگی چنداندامی | پایداری دست و بازو | دید نزدیک | دامنه انعطاف‌پذیری | دید دور | چابکی دستی | تجسم فضایی | مرتب‌سازی اطلاعات | ادراک عمق | تعادل عمومی بدن | استقامت بدنی | استحکام پویا | سرعت حرکت اندام‌ها | دقت کنترل | چابکی انگشتان | استدلال قیاسی | درک شفاهی</t>
+          <t>قدرت تنه | قدرت ایستا | هماهنگی چند عضو | ثبات دست و بازو | بینایی نزدیک | انعطاف‌پذیری دامنه حرکت | بینایی دور | مهارت دستی | تجسم | ترتیب‌دهی اطلاعات | درک عمق | تعادل کلی بدن | استقامت | قدرت پویا | سرعت حرکت اعضا | دقت کنترل | مهارت انگشتان | استدلال قیاسی | درک شفاهی</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>بناها و بلوک‌چین‌ها | نجاران | بناهای سیمان‌کار و پرداخت‌کاران بتن | کارگران ساختمانی | نصابان صفحات گچی و تایل سقف | کف‌پوش‌کاران به جز فرش، چوب و تایل‌های سخت | کمک‌نجاران | کارگران کمکی استخراج | کمک‌نصابان و کارگران کمکی تعمیرات و نگهداری | کمک‌نقاشان، کمک‌کاغذدیواری‌کاران، کمک‌گچ‌کاران و کمک‌سیمان‌کاران | کمک‌لوله‌گذاران، کمک‌لوله‌کش‌ها، کمک‌نصابان لوله و بخار | کارگران کمکی خطوط تولید | کمک‌ایزوگام‌کاران و کمک‌عایق‌کاران سقف | عایق‌کاران کف، سقف و دیوار | گچ‌کاران و سیمان‌کاران سنتی | تعمیرکاران مصالح نسوز به جز بناهای آجرنسوز | سنگ‌تراشان و سنگ‌چین‌ها | اسکلت‌سازان و نصابان سازه‌های فولادی | موزائیک‌سازان و پرداخت‌کاران سنگ و موزائیک | کاشی‌کاران و سنگ‌کاران</t>
+          <t>بنایان و سفت‌کاران ساختمان | نجاران و درودگران | بتن‌ریزان و پرداخت‌کاران بتن | کارگران ساختمانی | نصابان دیوار کاذب و تایل سقف | کف‌پوش‌کاران به‌جز فرش، چوب و کاشی سخت | کمک‌نجاران | کارگران کمکی استخراج معدن | کارگران کمکی نصب، نگهداری و تعمیرات | کمک‌نقاشان، کمک‌کاغذدیواری‌کاران، کمک‌گچ‌کاران و کمک‌سیمان‌کاران | کمک‌لوله‌گذاران، کمک‌لوله‌کش‌ها، کمک‌نصابان لوله و بخار | کمک‌کارگران خطوط تولید | کمک‌ایزوگام‌کاران و کمک‌عایق‌کاران سقف | عایق‌کاران کف، سقف و دیوار | سفیدکاران و گچ‌کاران نما | تعمیرکاران و نسوزکاران مواد دیرگداز صنعتی | سنگ‌کاران ساختمانی | اسکلت‌سازان و نصابان سازه‌های فولادی | موزاییک‌کاران و پرداخت‌کاران terrazzo | کاشی‌کاران و سنگ‌کاران ظریف</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,17 +679,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>نظارت | تفکر انتقادی | سخن گفتن | شنیدن فعال</t>
+          <t>نظارت | تفکر انتقادی | سخن گفتن | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>ساخت‌وساز و ابنیه | مکانیک | ریاضیات | حمل‌ونقل | زبان انگلیسی | خدمات مشتریان و خدمات فردی | تولید و فرآوری | طراحی | ایمنی و امنیت عمومی | مدیریت و امور اداری | آموزش و تدریس | مخابرات</t>
+          <t>ساختمان و ساخت‌وساز | مکانیک | ریاضیات | حمل و نقل | زبان انگلیسی | خدمات مشتری و شخصی | تولید و فرآوری | طراحی | ایمنی و امنیت عمومی | مدیریت و اداره | آموزش و پرورش | مخابرات</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>دید نزدیک | پایداری دست و بازو | چابکی دستی | حساسیت به مسئله | دامنه انعطاف‌پذیری | استحکام ایستا | هماهنگی چنداندامی | وضوح گفتار | تشخیص گفتار | ادراک عمق | استحکام بالاتنه | زمان واکنش | دقت کنترل | چابکی انگشتان | توجه انتخابی | تجسم فضایی | انعطاف‌پذیری طبقه‌بندی | مرتب‌سازی اطلاعات | استدلال استقرایی | استدلال قیاسی | بیان شفاهی | درک شفاهی</t>
+          <t>بینایی نزدیک | ثبات دست و بازو | مهارت دستی | حساسیت به مسئله | انعطاف‌پذیری دامنه حرکت | قدرت ایستا | هماهنگی چند عضو | وضوح گفتار | تشخیص گفتار | درک عمق | قدرت تنه | زمان عکس‌العمل | دقت کنترل | مهارت انگشتان | توجه انتخابی | تجسم | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | استدلال استقرایی | استدلال قیاسی | بیان شفاهی | درک شفاهی</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>دیگ‌سازان صنعتی | بناها و بلوک‌چین‌ها | کابینت‌سازان و نجاران کارگاهی | نجاران | بناهای سیمان‌کار و پرداخت‌کاران بتن | نصابان صفحات گچی و تایل سقف | کمک‌بناها، کمک‌بلوک‌چین‌ها، کمک‌سنگ‌تراشان و کمک‌نصابان کاشی و مرمر | کمک‌برق‌کاران | کارگران کمکی استخراج | کمک‌نصابان و کارگران کمکی تعمیرات و نگهداری | کمک‌نقاشان، کمک‌کاغذدیواری‌کاران، کمک‌گچ‌کاران و کمک‌سیمان‌کاران | کمک‌لوله‌گذاران، کمک‌لوله‌کش‌ها، کمک‌نصابان لوله و بخار | کارگران کمکی خطوط تولید | کمک‌ایزوگام‌کاران و کمک‌عایق‌کاران سقف | خط‌کشان و علامت‌گذاران فلز و پلاستیک | گچ‌کاران و سیمان‌کاران سنتی | آرماتوربندان و نصابان میلگرد سازه | اسکلت‌سازان و نصابان سازه‌های فولادی | سازندگان و مونتاژکاران قطعات فلزی سازه | موزائیک‌سازان و پرداخت‌کاران سنگ و موزائیک</t>
+          <t>دیگ‌سازان و مخزن‌سازان صنعتی | بنایان و سفت‌کاران ساختمان | کابینت‌سازان و نجاران کارگاهی | نجاران و درودگران | بتن‌ریزان و پرداخت‌کاران بتن | نصابان دیوار کاذب و تایل سقف | کمک‌بناها، کمک‌بلوک‌چین‌ها، کمک‌سنگ‌تراشان و کمک‌نصابان کاشی و مرمر | کمک‌برق‌کاران | کارگران کمکی استخراج معدن | کارگران کمکی نصب، نگهداری و تعمیرات | کمک‌نقاشان، کمک‌کاغذدیواری‌کاران، کمک‌گچ‌کاران و کمک‌سیمان‌کاران | کمک‌لوله‌گذاران، کمک‌لوله‌کش‌ها، کمک‌نصابان لوله و بخار | کمک‌کارگران خطوط تولید | کمک‌ایزوگام‌کاران و کمک‌عایق‌کاران سقف | خط‌کش‌ها و نشانه‌گذاران قطعات فلزی و پلاستیکی | سفیدکاران و گچ‌کاران نما | آرماتوربندان و نصابان میلگرد | اسکلت‌سازان و نصابان سازه‌های فولادی | سازندگان و مونتاژکاران سازه‌های فلزی | موزاییک‌کاران و پرداخت‌کاران terrazzo</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -731,22 +731,22 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>نرم‌افزار طراحی و نقشه‌کشی به کمک رایانه | Microsoft Excel | نرم‌افزار Microsoft Office | نرم‌افزار ثبت سوابق | نرم‌افزار تولید گزارش</t>
+          <t>نرم‌افزار نقشه‌کشی یا طراحی به کمک کامپیوتر | Microsoft Excel | نرم‌افزار Microsoft Office | نرم‌افزار ثبت سوابق | نرم‌افزار تولید گزارش</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | تفکر انتقادی</t>
+          <t>گوش دادن فعال | سخن گفتن | تفکر انتقادی</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ساخت‌وساز و ابنیه | مکانیک | ایمنی و امنیت عمومی | طراحی | خدمات مشتریان و خدمات فردی | مدیریت و امور اداری | آموزش و تدریس | زبان انگلیسی | ریاضیات | مهندسی و فناوری | فیزیک | حمل‌ونقل</t>
+          <t>ساختمان و ساخت‌وساز | مکانیک | ایمنی و امنیت عمومی | طراحی | خدمات مشتری و شخصی | مدیریت و اداره | آموزش و پرورش | زبان انگلیسی | ریاضیات | مهندسی و فناوری | فیزیک | حمل و نقل</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>دید نزدیک | چابکی دستی | دامنه انعطاف‌پذیری | چابکی انگشتان | پایداری دست و بازو | حساسیت به مسئله | دقت کنترل | هماهنگی چنداندامی | استحکام بالاتنه | تمایز رنگ‌های بینایی | بیان شفاهی | درک شفاهی | تشخیص گفتار | توجه انتخابی | مرتب‌سازی اطلاعات | استدلال قیاسی | وضوح گفتار | تعادل عمومی بدن | تجسم فضایی</t>
+          <t>بینایی نزدیک | مهارت دستی | انعطاف‌پذیری دامنه حرکت | مهارت انگشتان | ثبات دست و بازو | حساسیت به مسئله | دقت کنترل | هماهنگی چند عضو | قدرت تنه | تشخیص رنگ بصری | بیان شفاهی | درک شفاهی | تشخیص گفتار | توجه انتخابی | ترتیب‌دهی اطلاعات | استدلال قیاسی | وضوح گفتار | تعادل کلی بدن | تجسم</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>مونتاژکاران سازه، سطوح، مهاربندی و سیستم‌های هواپیما | دیگ‌سازان صنعتی | نجاران | تعمیرکاران الکتروموتورها، ابزارهای برقی و تجهیزات وابسته | نصابان و تعمیرکاران خطوط انتقال و توزیع برق | مونتاژکاران تجهیزات برقی و الکترونیکی | نصابان و تعمیرکاران تجهیزات الکتریکی و الکترونیکی ادوات حمل‌ونقل | برق‌کاران | کمک‌نجاران | کارگران کمکی استخراج | کمک‌نصابان و کارگران کمکی تعمیرات و نگهداری | کمک‌نقاشان، کمک‌کاغذدیواری‌کاران، کمک‌گچ‌کاران و کمک‌سیمان‌کاران | کمک‌لوله‌گذاران، کمک‌لوله‌کش‌ها، کمک‌نصابان لوله و بخار | تکنسین‌های روشنایی | کارگران عمومی تعمیرات و نگهداری | نصابان و مستقرکنندگان ماشین‌آلات صنعتی (میلرایت‌ها) | لوله‌کش‌ها، نصابان لوله‌های صنعتی و تأسیسات بخار | دکل‌بندان و طناب‌کاران | اسکلت‌سازان و نصابان سازه‌های فولادی | سازندگان و مونتاژکاران قطعات فلزی سازه</t>
+          <t>مونتاژکاران سازه، سطوح، مهاربندی و سیستم‌های هواپیما | دیگ‌سازان و مخزن‌سازان صنعتی | نجاران و درودگران | تعمیرکاران موتورهای الکتریکی، ابزارهای برقی و تجهیزات وابسته | تکنسین‌ها و سیم‌بانان خطوط انتقال و توزیع برق | مونتاژکاران تجهیزات الکتریکی و الکترونیکی | نصاب و تعمیرکار تجهیزات الکتریکی و الکترونیکی وسایل نقلیه | برق‌کاران | کمک‌نجاران | کارگران کمکی استخراج معدن | کارگران کمکی نصب، نگهداری و تعمیرات | کمک‌نقاشان، کمک‌کاغذدیواری‌کاران، کمک‌گچ‌کاران و کمک‌سیمان‌کاران | کمک‌لوله‌گذاران، کمک‌لوله‌کش‌ها، کمک‌نصابان لوله و بخار | تکنسین‌های نورپردازی | کارگران عمومی تعمیرات و نگهداری تاسیسات | ماشین‌سازان و متخصصان نصب ماشین‌آلات سنگین [میل‌رایت] | لوله‌کش‌ها، لوله‌کش‌های صنعتی و نصابان خطوط بخار | ریگرها و تکنسین‌های مهاربندی و جابه‌جایی بار | اسکلت‌سازان و نصابان سازه‌های فولادی | سازندگان و مونتاژکاران سازه‌های فلزی</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ساخت‌وساز و ابنیه | زبان انگلیسی</t>
+          <t>ساختمان و ساخت‌وساز | زبان انگلیسی</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>پایداری دست و بازو | تعادل عمومی بدن | دامنه انعطاف‌پذیری | استحکام بالاتنه | استحکام ایستا | چابکی دستی | هماهنگی عمومی بدن | هماهنگی چنداندامی | تشخیص گفتار | دید دور | دید نزدیک | استقامت بدنی | استحکام پویا | چابکی انگشتان | بیان شفاهی | درک شفاهی</t>
+          <t>ثبات دست و بازو | تعادل کلی بدن | انعطاف‌پذیری دامنه حرکت | قدرت تنه | قدرت ایستا | مهارت دستی | هماهنگی کلی بدن | هماهنگی چند عضو | تشخیص گفتار | بینایی دور | بینایی نزدیک | استقامت | قدرت پویا | مهارت انگشتان | بیان شفاهی | درک شفاهی</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>بناها و بلوک‌چین‌ها | نجاران | بناهای سیمان‌کار و پرداخت‌کاران بتن | کارگران ساختمانی | نصابان صفحات گچی و تایل سقف | کمک‌بناها، کمک‌بلوک‌چین‌ها، کمک‌سنگ‌تراشان و کمک‌نصابان کاشی و مرمر | کمک‌نجاران | کمک‌برق‌کاران | کارگران کمکی استخراج | کمک‌نصابان و کارگران کمکی تعمیرات و نگهداری | کمک‌لوله‌گذاران، کمک‌لوله‌کش‌ها، کمک‌نصابان لوله و بخار | کارگران کمکی خطوط تولید | کمک‌ایزوگام‌کاران و کمک‌عایق‌کاران سقف | عایق‌کاران کف، سقف و دیوار | نقاشان ساختمان و تأسیسات | کارگران رنگ‌کاری صنعتی، پوشش‌دهی و تزئینی | کاغذدیواری‌کاران | گچ‌کاران و سیمان‌کاران سنتی | ایزوگام‌کاران و نصابان پوشش سقف | موزائیک‌سازان و پرداخت‌کاران سنگ و موزائیک</t>
+          <t>بنایان و سفت‌کاران ساختمان | نجاران و درودگران | بتن‌ریزان و پرداخت‌کاران بتن | کارگران ساختمانی | نصابان دیوار کاذب و تایل سقف | کمک‌بناها، کمک‌بلوک‌چین‌ها، کمک‌سنگ‌تراشان و کمک‌نصابان کاشی و مرمر | کمک‌نجاران | کمک‌برق‌کاران | کارگران کمکی استخراج معدن | کارگران کمکی نصب، نگهداری و تعمیرات | کمک‌لوله‌گذاران، کمک‌لوله‌کش‌ها، کمک‌نصابان لوله و بخار | کمک‌کارگران خطوط تولید | کمک‌ایزوگام‌کاران و کمک‌عایق‌کاران سقف | عایق‌کاران کف، سقف و دیوار | نقاشان ساختمان و تاسیسات | کارگران رنگ‌کاری، پوشش‌دهی و تزیین قطعات | نصابان کاغذ دیواری | سفیدکاران و گچ‌کاران نما | عایق‌کاران و نصابان پوشش‌های سقفی | موزاییک‌کاران و پرداخت‌کاران terrazzo</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,17 +850,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>نظارت | شنیدن فعال | تفکر انتقادی | درک مطلب | سخن گفتن</t>
+          <t>نظارت | گوش دادن فعال | تفکر انتقادی | درک مطلب | سخن گفتن</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ساخت‌وساز و ابنیه | خدمات مشتریان و خدمات فردی | مکانیک | ریاضیات | زبان انگلیسی | مدیریت و امور اداری</t>
+          <t>ساختمان و ساخت‌وساز | خدمات مشتری و شخصی | مکانیک | ریاضیات | زبان انگلیسی | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>چابکی دستی | هماهنگی چنداندامی | پایداری دست و بازو | استحکام بالاتنه | دامنه انعطاف‌پذیری | دید نزدیک | درک شفاهی | حساسیت به مسئله | تجسم فضایی | تشخیص گفتار | استحکام ایستا | دقت کنترل | چابکی انگشتان | مرتب‌سازی اطلاعات | بیان شفاهی</t>
+          <t>مهارت دستی | هماهنگی چند عضو | ثبات دست و بازو | قدرت تنه | انعطاف‌پذیری دامنه حرکت | بینایی نزدیک | درک شفاهی | حساسیت به مسئله | تجسم | تشخیص گفتار | قدرت ایستا | دقت کنترل | مهارت انگشتان | ترتیب‌دهی اطلاعات | بیان شفاهی</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>دیگ‌سازان صنعتی | نجاران | کارگران ساختمانی | نصابان صفحات گچی و تایل سقف | برق‌کاران | کمک‌بناها، کمک‌بلوک‌چین‌ها، کمک‌سنگ‌تراشان و کمک‌نصابان کاشی و مرمر | کمک‌نجاران | کمک‌برق‌کاران | کارگران کمکی استخراج | کمک‌نصابان و کارگران کمکی تعمیرات و نگهداری | کمک‌نقاشان، کمک‌کاغذدیواری‌کاران، کمک‌گچ‌کاران و کمک‌سیمان‌کاران | کمک‌ایزوگام‌کاران و کمک‌عایق‌کاران سقف | عایق‌کاران کف، سقف و دیوار | کارگران عمومی تعمیرات و نگهداری | نصابان و مستقرکنندگان ماشین‌آلات صنعتی (میلرایت‌ها) | لوله‌گذاران | لوله‌کش‌ها، نصابان لوله‌های صنعتی و تأسیسات بخار | سرویس‌کاران مخازن فاضلاب و پاک‌کنندگان لوله‌های فاضلاب | ورق‌کاران فلزی | اسکلت‌سازان و نصابان سازه‌های فولادی</t>
+          <t>دیگ‌سازان و مخزن‌سازان صنعتی | نجاران و درودگران | کارگران ساختمانی | نصابان دیوار کاذب و تایل سقف | برق‌کاران | کمک‌بناها، کمک‌بلوک‌چین‌ها، کمک‌سنگ‌تراشان و کمک‌نصابان کاشی و مرمر | کمک‌نجاران | کمک‌برق‌کاران | کارگران کمکی استخراج معدن | کارگران کمکی نصب، نگهداری و تعمیرات | کمک‌نقاشان، کمک‌کاغذدیواری‌کاران، کمک‌گچ‌کاران و کمک‌سیمان‌کاران | کمک‌ایزوگام‌کاران و کمک‌عایق‌کاران سقف | عایق‌کاران کف، سقف و دیوار | کارگران عمومی تعمیرات و نگهداری تاسیسات | ماشین‌سازان و متخصصان نصب ماشین‌آلات سنگین [میل‌رایت] | لوله‌گذاران خطوط انتقال | لوله‌کش‌ها، لوله‌کش‌های صنعتی و نصابان خطوط بخار | سرویس‌کاران مخازن سپتیک و لایروبان مجاری فاضلاب | کارگران ورق‌کاری فلزی | اسکلت‌سازان و نصابان سازه‌های فولادی</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>نظارت | شنیدن فعال</t>
+          <t>نظارت | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ساخت‌وساز و ابنیه | مدیریت و امور اداری | خدمات مشتریان و خدمات فردی | ایمنی و امنیت عمومی | ریاضیات | حمل‌ونقل | مکانیک | آموزش و تدریس</t>
+          <t>ساختمان و ساخت‌وساز | مدیریت و اداره | خدمات مشتری و شخصی | ایمنی و امنیت عمومی | ریاضیات | حمل و نقل | مکانیک | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>استحکام بالاتنه | تعادل عمومی بدن | چابکی دستی | هماهنگی چنداندامی | وضوح گفتار | حساسیت به مسئله | تجسم فضایی | پایداری دست و بازو | چابکی انگشتان | تشخیص گفتار | ادراک عمق | دامنه انعطاف‌پذیری | استحکام ایستا | دید دور | هماهنگی عمومی بدن | استقامت بدنی | انعطاف‌پذیری بستن | مرتب‌سازی اطلاعات | بیان شفاهی | درک شفاهی</t>
+          <t>قدرت تنه | تعادل کلی بدن | مهارت دستی | هماهنگی چند عضو | وضوح گفتار | حساسیت به مسئله | تجسم | ثبات دست و بازو | مهارت انگشتان | تشخیص گفتار | درک عمق | انعطاف‌پذیری دامنه حرکت | قدرت ایستا | بینایی دور | هماهنگی کلی بدن | استقامت | انعطاف‌پذیری بستار | ترتیب‌دهی اطلاعات | بیان شفاهی | درک شفاهی</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>نجاران | بناهای سیمان‌کار و پرداخت‌کاران بتن | کارگران ساختمانی | نصابان صفحات گچی و تایل سقف | کف‌پوش‌کاران به جز فرش، چوب و تایل‌های سخت | کمک‌بناها، کمک‌بلوک‌چین‌ها، کمک‌سنگ‌تراشان و کمک‌نصابان کاشی و مرمر | کمک‌نجاران | کمک‌برق‌کاران | کارگران کمکی استخراج | کمک‌نصابان و کارگران کمکی تعمیرات و نگهداری | کمک‌نقاشان، کمک‌کاغذدیواری‌کاران، کمک‌گچ‌کاران و کمک‌سیمان‌کاران | کمک‌لوله‌گذاران، کمک‌لوله‌کش‌ها، کمک‌نصابان لوله و بخار | عایق‌کاران کف، سقف و دیوار | عایق‌کاران تأسیسات مکانیکی | نقاشان ساختمان و تأسیسات | گچ‌کاران و سیمان‌کاران سنتی | ایزوگام‌کاران و نصابان پوشش سقف | اسکلت‌سازان و نصابان سازه‌های فولادی | موزائیک‌سازان و پرداخت‌کاران سنگ و موزائیک | کاشی‌کاران و سنگ‌کاران</t>
+          <t>نجاران و درودگران | بتن‌ریزان و پرداخت‌کاران بتن | کارگران ساختمانی | نصابان دیوار کاذب و تایل سقف | کف‌پوش‌کاران به‌جز فرش، چوب و کاشی سخت | کمک‌بناها، کمک‌بلوک‌چین‌ها، کمک‌سنگ‌تراشان و کمک‌نصابان کاشی و مرمر | کمک‌نجاران | کمک‌برق‌کاران | کارگران کمکی استخراج معدن | کارگران کمکی نصب، نگهداری و تعمیرات | کمک‌نقاشان، کمک‌کاغذدیواری‌کاران، کمک‌گچ‌کاران و کمک‌سیمان‌کاران | کمک‌لوله‌گذاران، کمک‌لوله‌کش‌ها، کمک‌نصابان لوله و بخار | عایق‌کاران کف، سقف و دیوار | عایق‌کاران تاسیسات مکانیکی | نقاشان ساختمان و تاسیسات | سفیدکاران و گچ‌کاران نما | عایق‌کاران و نصابان پوشش‌های سقفی | اسکلت‌سازان و نصابان سازه‌های فولادی | موزاییک‌کاران و پرداخت‌کاران terrazzo | کاشی‌کاران و سنگ‌کاران ظریف</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,17 +964,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>نظارت | شنیدن فعال | تفکر انتقادی | درک مطلب | سخن گفتن</t>
+          <t>نظارت | گوش دادن فعال | تفکر انتقادی | درک مطلب | سخن گفتن</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ساخت‌وساز و ابنیه | مکانیک | زبان انگلیسی | ایمنی و امنیت عمومی | ریاضیات | تولید و فرآوری</t>
+          <t>ساختمان و ساخت‌وساز | مکانیک | زبان انگلیسی | ایمنی و امنیت عمومی | ریاضیات | تولید و فرآوری</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>چابکی دستی | چابکی انگشتان | پایداری دست و بازو | هماهنگی چنداندامی | دقت کنترل | استحکام ایستا | استحکام بالاتنه | استقامت بدنی | دید نزدیک | دید دور | ادراک عمق | هماهنگی عمومی بدن | تعادل عمومی بدن | دامنه انعطاف‌پذیری | زمان واکنش | حساسیت به مسئله | درک شفاهی | توجه انتخابی</t>
+          <t>مهارت دستی | مهارت انگشتان | ثبات دست و بازو | هماهنگی چند عضو | دقت کنترل | قدرت ایستا | قدرت تنه | استقامت | بینایی نزدیک | بینایی دور | درک عمق | هماهنگی کلی بدن | تعادل کلی بدن | انعطاف‌پذیری دامنه حرکت | زمان عکس‌العمل | حساسیت به مسئله | درک شفاهی | توجه انتخابی</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>کمک‌نجاران | کمک‌برق‌کاران | کمک‌لوله‌گذاران، کمک‌لوله‌کش‌ها، کمک‌نصابان لوله و بخار | کمک‌ایزوگام‌کاران و کمک‌عایق‌کاران سقف | کمک‌نقاشان، کمک‌کاغذدیواری‌کاران، کمک‌گچ‌کاران و کمک‌سیمان‌کاران | کمک‌بناها، کمک‌بلوک‌چین‌ها، کمک‌سنگ‌تراشان و کمک‌نصابان کاشی و مرمر | کارگران ساختمانی | نجاران | برق‌کاران | لوله‌کش‌ها، نصابان لوله‌های صنعتی و تأسیسات بخار | ورق‌کاران فلزی | شیشه‌بران و نصابان شیشه | ایزوگام‌کاران و نصابان پوشش سقف | عایق‌کاران تأسیسات مکانیکی | اسکلت‌سازان و نصابان سازه‌های فولادی | آرماتوربندان و نصابان میلگرد سازه | نصابان صفحات گچی و تایل سقف | نقاشان ساختمان و تأسیسات | سرپرستان رده‌اول کارگران ساختمانی و استخراج | کمک‌نصابان و کارگران کمکی تعمیرات و نگهداری</t>
+          <t>کمک‌نجاران | کمک‌برق‌کاران | کمک‌لوله‌گذاران، کمک‌لوله‌کش‌ها، کمک‌نصابان لوله و بخار | کمک‌ایزوگام‌کاران و کمک‌عایق‌کاران سقف | کمک‌نقاشان، کمک‌کاغذدیواری‌کاران، کمک‌گچ‌کاران و کمک‌سیمان‌کاران | کمک‌بناها، کمک‌بلوک‌چین‌ها، کمک‌سنگ‌تراشان و کمک‌نصابان کاشی و مرمر | کارگران ساختمانی | نجاران و درودگران | برق‌کاران | لوله‌کش‌ها، لوله‌کش‌های صنعتی و نصابان خطوط بخار | کارگران ورق‌کاری فلزی | شیشه‌بران و نصابان شیشه | عایق‌کاران و نصابان پوشش‌های سقفی | عایق‌کاران تاسیسات مکانیکی | اسکلت‌سازان و نصابان سازه‌های فولادی | آرماتوربندان و نصابان میلگرد | نصابان دیوار کاذب و تایل سقف | نقاشان ساختمان و تاسیسات | سرپرستان رده‌اول مشاغل ساختمانی، عمرانی و استخراج | کارگران کمکی نصب، نگهداری و تعمیرات</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | شنیدن فعال | سخن گفتن | نگارش | یادگیری فعال | نظارت | راهبردهای یادگیری | ریاضیات</t>
+          <t>درک مطلب | تفکر انتقادی | گوش دادن فعال | سخن گفتن | نگارش | یادگیری فعال | نظارت | راهبردهای یادگیری | ریاضیات</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ساخت‌وساز و ابنیه | ایمنی و امنیت عمومی | زبان انگلیسی | خدمات مشتریان و خدمات فردی | طراحی | حقوق و مقررات دولتی | ریاضیات | مدیریت و امور اداری | مکانیک | امور اداری و دفتری | رایانه و الکترونیک | مهندسی و فناوری | آموزش و تدریس</t>
+          <t>ساختمان و ساخت‌وساز | ایمنی و امنیت عمومی | زبان انگلیسی | خدمات مشتری و شخصی | طراحی | قانون و دولت | ریاضیات | مدیریت و اداره | مکانیک | اداری | رایانه و الکترونیک | مهندسی و فناوری | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | درک کتبی | بیان شفاهی | استدلال استقرایی | استدلال قیاسی | درک شفاهی | بیان کتبی | دید نزدیک | تشخیص گفتار | وضوح گفتار | مرتب‌سازی اطلاعات | دید دور | توجه انتخابی | انعطاف‌پذیری بستن | انعطاف‌پذیری طبقه‌بندی | تمایز رنگ‌های بینایی | تجسم فضایی | سرعت ادراک | روانی ایده‌ها</t>
+          <t>حساسیت به مسئله | درک کتبی | بیان شفاهی | استدلال استقرایی | استدلال قیاسی | درک شفاهی | بیان کتبی | بینایی نزدیک | تشخیص گفتار | وضوح گفتار | ترتیب‌دهی اطلاعات | بینایی دور | توجه انتخابی | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | تشخیص رنگ بصری | تجسم | سرعت ادراکی | روانی ایده‌ها</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>معماران به جز معماران منظر و نیروی دریایی | بازرسان هوانوردی | کارشناسان و تکنسین‌های مهندسی عمران | مهندسان عمران | مدیران ساخت‌وساز | برق‌کاران | ممیزان انرژی | بازرسان انطباق زیست‌محیطی | مهندسان پیشگیری و حفاظت از حریق | سرپرستان رده‌اول کارگران ساختمانی و استخراج | بازرسان و محققان اموال دولتی | مهندسان بهداشت و ایمنی حرفه‌ای به جز مهندسان و بازرسان معدن | مهندسان صنایع | بازرسان، آزمون‌گران، درجه‌بندان، نمونه‌برداران و توزین‌کنندگان | کارگران عمومی تعمیرات و نگهداری | متخصصان بهداشت حرفه‌ای و ایمنی کار | لوله‌کش‌ها، نصابان لوله‌های صنعتی و تأسیسات بخار | مدیران پروژه‌های نصب انرژی خورشیدی | بازرسان ترابری | بازرسان وسایل نقلیه، تجهیزات و سامانه‌های ترابری به جز هوانوردی</t>
+          <t>مهندسان معمار، به‌جز معماران منظر و سازه‌های دریایی | بازرسان هوانوردی و فرودگاهی | کارشناسان و تکنسین‌های مهندسی عمران | مهندسان عمران | مدیران پروژه‌های ساختمانی | برق‌کاران | ممیزان انرژی | بازرسان رعایت ضوابط زیست‌محیطی | مهندسان پیشگیری و حفاظت از حریق | سرپرستان رده‌اول مشاغل ساختمانی، عمرانی و استخراج | بازرسان و ممیزان اموال دولتی | مهندسان بهداشت و ایمنی، به‌جز مهندسان و بازرسان ایمنی معدن | مهندسان صنایع | بازرسان، آزمونگران، تفکیک‌کنندگان، نمونه‌برداران و توزین‌گران | کارگران عمومی تعمیرات و نگهداری تاسیسات | کارشناسان بهداشت حرفه‌ای و ایمنی کار | لوله‌کش‌ها، لوله‌کش‌های صنعتی و نصابان خطوط بخار | مدیران اجرای پروژه‌های انرژی خورشیدی | بازرسان ترابری و حمل‌ونقل | بازرسان سامانه‌ها، تجهیزات و وسایل نقلیه ترابری (به‌جز هوانوردی)</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
